--- a/Data/Generic Bundesbank yield.xlsx
+++ b/Data/Generic Bundesbank yield.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alumni-my.sharepoint.com/personal/zbr894_ku_dk/Documents/OscarErnst-Heterogenous-spillover-ECB/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{1E0EAD6D-07DB-4C80-883A-34AC6D3AFF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25C78D86-271B-9645-94FE-21FCDFC3C31E}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{1E0EAD6D-07DB-4C80-883A-34AC6D3AFF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C82010A-ACEB-1E4F-95AE-800400EE5023}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19620" xr2:uid="{C61B667D-FFFD-4880-8CB5-595AC52861AE}"/>
   </bookViews>
@@ -445,7 +445,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>35642</v>
+        <v>35612</v>
       </c>
       <c r="C2">
         <v>3.3109999999999999</v>
@@ -453,7 +453,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>35671</v>
+        <v>35643</v>
       </c>
       <c r="C3">
         <v>3.4740000000000002</v>
@@ -461,7 +461,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>35703</v>
+        <v>35674</v>
       </c>
       <c r="C4">
         <v>3.5950000000000002</v>
@@ -469,7 +469,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>35734</v>
+        <v>35704</v>
       </c>
       <c r="C5">
         <v>3.9209999999999998</v>
@@ -477,7 +477,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>35762</v>
+        <v>35735</v>
       </c>
       <c r="C6">
         <v>4.0140000000000002</v>
@@ -485,7 +485,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>35795</v>
+        <v>35765</v>
       </c>
       <c r="C7">
         <v>3.9089999999999998</v>
@@ -493,7 +493,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>35825</v>
+        <v>35796</v>
       </c>
       <c r="C8">
         <v>3.673</v>
@@ -501,7 +501,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>35853</v>
+        <v>35827</v>
       </c>
       <c r="C9">
         <v>3.6549999999999998</v>
@@ -509,7 +509,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>35885</v>
+        <v>35855</v>
       </c>
       <c r="C10">
         <v>3.798</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>35915</v>
+        <v>35886</v>
       </c>
       <c r="C11">
         <v>3.8740000000000001</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>35944</v>
+        <v>35916</v>
       </c>
       <c r="C12">
         <v>3.734</v>
@@ -533,7 +533,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>35976</v>
+        <v>35947</v>
       </c>
       <c r="C13">
         <v>3.7970000000000002</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>36007</v>
+        <v>35977</v>
       </c>
       <c r="C14">
         <v>3.7440000000000002</v>
@@ -549,7 +549,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>36038</v>
+        <v>36008</v>
       </c>
       <c r="C15">
         <v>3.5</v>
@@ -557,7 +557,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>36068</v>
+        <v>36039</v>
       </c>
       <c r="C16">
         <v>3.4710000000000001</v>
@@ -565,7 +565,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>36098</v>
+        <v>36069</v>
       </c>
       <c r="C17">
         <v>3.4249999999999998</v>
@@ -573,7 +573,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>36129</v>
+        <v>36100</v>
       </c>
       <c r="C18">
         <v>3.347</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>36160</v>
+        <v>36130</v>
       </c>
       <c r="C19">
         <v>2.9590000000000001</v>
@@ -589,7 +589,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>36189</v>
+        <v>36161</v>
       </c>
       <c r="C20">
         <v>2.883</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>36217</v>
+        <v>36192</v>
       </c>
       <c r="C21">
         <v>3.016</v>
@@ -605,7 +605,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>36250</v>
+        <v>36220</v>
       </c>
       <c r="C22">
         <v>2.871</v>
@@ -613,7 +613,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>36280</v>
+        <v>36251</v>
       </c>
       <c r="C23">
         <v>2.6160000000000001</v>
@@ -621,7 +621,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>36311</v>
+        <v>36281</v>
       </c>
       <c r="C24">
         <v>2.6669999999999998</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>36341</v>
+        <v>36312</v>
       </c>
       <c r="C25">
         <v>2.8889999999999998</v>
@@ -637,7 +637,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>36371</v>
+        <v>36342</v>
       </c>
       <c r="C26">
         <v>2.9860000000000002</v>
@@ -645,7 +645,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>36403</v>
+        <v>36373</v>
       </c>
       <c r="C27">
         <v>3.0880000000000001</v>
@@ -653,7 +653,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>36433</v>
+        <v>36404</v>
       </c>
       <c r="C28">
         <v>3.1509999999999998</v>
@@ -661,7 +661,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>36462</v>
+        <v>36434</v>
       </c>
       <c r="C29">
         <v>3.4260000000000002</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>36494</v>
+        <v>36465</v>
       </c>
       <c r="C30">
         <v>3.5019999999999998</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>36525</v>
+        <v>36495</v>
       </c>
       <c r="C31">
         <v>3.661</v>
@@ -685,7 +685,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>36556</v>
+        <v>36526</v>
       </c>
       <c r="C32">
         <v>3.8879999999999999</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>36585</v>
+        <v>36557</v>
       </c>
       <c r="C33">
         <v>3.891</v>
@@ -701,7 +701,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>36616</v>
+        <v>36586</v>
       </c>
       <c r="C34">
         <v>4.1390000000000002</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>36644</v>
+        <v>36617</v>
       </c>
       <c r="C35">
         <v>4.3460000000000001</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
-        <v>36677</v>
+        <v>36647</v>
       </c>
       <c r="C36">
         <v>4.7380000000000004</v>
@@ -731,7 +731,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>36707</v>
+        <v>36678</v>
       </c>
       <c r="C37">
         <v>4.8710000000000004</v>
@@ -742,7 +742,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
-        <v>36738</v>
+        <v>36708</v>
       </c>
       <c r="C38">
         <v>5.0350000000000001</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
-        <v>36769</v>
+        <v>36739</v>
       </c>
       <c r="C39">
         <v>5.1390000000000002</v>
@@ -764,7 +764,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
-        <v>36798</v>
+        <v>36770</v>
       </c>
       <c r="C40">
         <v>5.093</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
-        <v>36830</v>
+        <v>36800</v>
       </c>
       <c r="C41">
         <v>5.1719999999999997</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
-        <v>36860</v>
+        <v>36831</v>
       </c>
       <c r="C42">
         <v>4.9480000000000004</v>
@@ -797,7 +797,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
-        <v>36889</v>
+        <v>36861</v>
       </c>
       <c r="C43">
         <v>4.63</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
-        <v>36922</v>
+        <v>36892</v>
       </c>
       <c r="C44">
         <v>4.4649999999999999</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
-        <v>36950</v>
+        <v>36923</v>
       </c>
       <c r="C45">
         <v>4.5250000000000004</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
-        <v>36980</v>
+        <v>36951</v>
       </c>
       <c r="C46">
         <v>4.2880000000000003</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
-        <v>37011</v>
+        <v>36982</v>
       </c>
       <c r="C47">
         <v>4.7469999999999999</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
-        <v>37042</v>
+        <v>37012</v>
       </c>
       <c r="C48">
         <v>4.3940000000000001</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
-        <v>37071</v>
+        <v>37043</v>
       </c>
       <c r="C49">
         <v>4.2649999999999997</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
-        <v>37103</v>
+        <v>37073</v>
       </c>
       <c r="C50">
         <v>4.1749999999999998</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
-        <v>37134</v>
+        <v>37104</v>
       </c>
       <c r="C51">
         <v>3.996</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
-        <v>37162</v>
+        <v>37135</v>
       </c>
       <c r="C52">
         <v>3.456</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
-        <v>37195</v>
+        <v>37165</v>
       </c>
       <c r="C53">
         <v>3.2069999999999999</v>
@@ -918,7 +918,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
-        <v>37225</v>
+        <v>37196</v>
       </c>
       <c r="C54">
         <v>3.1629999999999998</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
-        <v>37256</v>
+        <v>37226</v>
       </c>
       <c r="C55">
         <v>3.3090000000000002</v>
@@ -940,7 +940,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
-        <v>37287</v>
+        <v>37257</v>
       </c>
       <c r="C56">
         <v>3.504</v>
@@ -951,7 +951,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
-        <v>37315</v>
+        <v>37288</v>
       </c>
       <c r="C57">
         <v>3.4889999999999999</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
-        <v>37344</v>
+        <v>37316</v>
       </c>
       <c r="C58">
         <v>3.9079999999999999</v>
@@ -973,7 +973,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
-        <v>37376</v>
+        <v>37347</v>
       </c>
       <c r="C59">
         <v>3.6779999999999999</v>
@@ -984,7 +984,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
-        <v>37407</v>
+        <v>37377</v>
       </c>
       <c r="C60">
         <v>3.9729999999999999</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
-        <v>37435</v>
+        <v>37408</v>
       </c>
       <c r="C61">
         <v>3.681</v>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
-        <v>37468</v>
+        <v>37438</v>
       </c>
       <c r="C62">
         <v>3.4079999999999999</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
-        <v>37498</v>
+        <v>37469</v>
       </c>
       <c r="C63">
         <v>3.33</v>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
-        <v>37529</v>
+        <v>37500</v>
       </c>
       <c r="C64">
         <v>3.0430000000000001</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
-        <v>37560</v>
+        <v>37530</v>
       </c>
       <c r="C65">
         <v>3.0270000000000001</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
-        <v>37589</v>
+        <v>37561</v>
       </c>
       <c r="B66">
         <v>2.9</v>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
-        <v>37621</v>
+        <v>37591</v>
       </c>
       <c r="B67">
         <v>2.76</v>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
-        <v>37652</v>
+        <v>37622</v>
       </c>
       <c r="B68">
         <v>2.6539999999999999</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
-        <v>37680</v>
+        <v>37653</v>
       </c>
       <c r="B69">
         <v>2.38</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
-        <v>37711</v>
+        <v>37681</v>
       </c>
       <c r="B70">
         <v>2.36</v>
@@ -1120,7 +1120,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
-        <v>37741</v>
+        <v>37712</v>
       </c>
       <c r="B71">
         <v>2.3780000000000001</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
-        <v>37771</v>
+        <v>37742</v>
       </c>
       <c r="B72">
         <v>2.1440000000000001</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
-        <v>37802</v>
+        <v>37773</v>
       </c>
       <c r="B73">
         <v>2.0190000000000001</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
-        <v>37833</v>
+        <v>37803</v>
       </c>
       <c r="B74">
         <v>2.0670000000000002</v>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
-        <v>37862</v>
+        <v>37834</v>
       </c>
       <c r="B75">
         <v>2.1240000000000001</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
-        <v>37894</v>
+        <v>37865</v>
       </c>
       <c r="B76">
         <v>2.0329999999999999</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
-        <v>37925</v>
+        <v>37895</v>
       </c>
       <c r="B77">
         <v>2.141</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
-        <v>37953</v>
+        <v>37926</v>
       </c>
       <c r="B78">
         <v>2.1659999999999999</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
-        <v>37986</v>
+        <v>37956</v>
       </c>
       <c r="B79">
         <v>2.089</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
-        <v>38016</v>
+        <v>37987</v>
       </c>
       <c r="B80">
         <v>2.0720000000000001</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
-        <v>38044</v>
+        <v>38018</v>
       </c>
       <c r="B81">
         <v>1.9830000000000001</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
-        <v>38077</v>
+        <v>38047</v>
       </c>
       <c r="B82">
         <v>1.9039999999999999</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
-        <v>38107</v>
+        <v>38078</v>
       </c>
       <c r="B83">
         <v>2.0489999999999999</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
-        <v>38138</v>
+        <v>38108</v>
       </c>
       <c r="B84">
         <v>2.0840000000000001</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
-        <v>38168</v>
+        <v>38139</v>
       </c>
       <c r="B85">
         <v>2.1030000000000002</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
-        <v>38198</v>
+        <v>38169</v>
       </c>
       <c r="B86">
         <v>2.1179999999999999</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
-        <v>38230</v>
+        <v>38200</v>
       </c>
       <c r="B87">
         <v>2.1</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
-        <v>38260</v>
+        <v>38231</v>
       </c>
       <c r="B88">
         <v>2.1360000000000001</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
-        <v>38289</v>
+        <v>38261</v>
       </c>
       <c r="B89">
         <v>2.1459999999999999</v>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
-        <v>38321</v>
+        <v>38292</v>
       </c>
       <c r="B90">
         <v>2.1469999999999998</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
-        <v>38352</v>
+        <v>38322</v>
       </c>
       <c r="B91">
         <v>2.1389999999999998</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
-        <v>38383</v>
+        <v>38353</v>
       </c>
       <c r="B92">
         <v>2.1219999999999999</v>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
-        <v>38411</v>
+        <v>38384</v>
       </c>
       <c r="B93">
         <v>2.1379999999999999</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
-        <v>38442</v>
+        <v>38412</v>
       </c>
       <c r="B94">
         <v>2.133</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
-        <v>38471</v>
+        <v>38443</v>
       </c>
       <c r="B95">
         <v>2.0790000000000002</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
-        <v>38503</v>
+        <v>38473</v>
       </c>
       <c r="B96">
         <v>2.0750000000000002</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
-        <v>38533</v>
+        <v>38504</v>
       </c>
       <c r="B97">
         <v>2.0609999999999999</v>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
-        <v>38562</v>
+        <v>38534</v>
       </c>
       <c r="B98">
         <v>2.0939999999999999</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
-        <v>38595</v>
+        <v>38565</v>
       </c>
       <c r="B99">
         <v>2.0990000000000002</v>
@@ -1526,7 +1526,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
-        <v>38625</v>
+        <v>38596</v>
       </c>
       <c r="B100">
         <v>2.1309999999999998</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
-        <v>38656</v>
+        <v>38626</v>
       </c>
       <c r="B101">
         <v>2.2829999999999999</v>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
-        <v>38686</v>
+        <v>38657</v>
       </c>
       <c r="B102">
         <v>2.5110000000000001</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
-        <v>38716</v>
+        <v>38687</v>
       </c>
       <c r="B103">
         <v>2.54</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
-        <v>38748</v>
+        <v>38718</v>
       </c>
       <c r="B104">
         <v>2.6179999999999999</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
-        <v>38776</v>
+        <v>38749</v>
       </c>
       <c r="B105">
         <v>2.6619999999999999</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
-        <v>38807</v>
+        <v>38777</v>
       </c>
       <c r="B106">
         <v>2.8359999999999999</v>
@@ -1624,7 +1624,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
-        <v>38835</v>
+        <v>38808</v>
       </c>
       <c r="B107">
         <v>2.8660000000000001</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
-        <v>38868</v>
+        <v>38838</v>
       </c>
       <c r="B108">
         <v>2.9449999999999998</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
-        <v>38898</v>
+        <v>38869</v>
       </c>
       <c r="B109">
         <v>3.0640000000000001</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
-        <v>38929</v>
+        <v>38899</v>
       </c>
       <c r="B110">
         <v>3.1669999999999998</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
-        <v>38960</v>
+        <v>38930</v>
       </c>
       <c r="B111">
         <v>3.2959999999999998</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
-        <v>38989</v>
+        <v>38961</v>
       </c>
       <c r="B112">
         <v>3.4209999999999998</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
-        <v>39021</v>
+        <v>38991</v>
       </c>
       <c r="B113">
         <v>3.5</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
-        <v>39051</v>
+        <v>39022</v>
       </c>
       <c r="B114">
         <v>3.581</v>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
-        <v>39080</v>
+        <v>39052</v>
       </c>
       <c r="B115">
         <v>3.6949999999999998</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
-        <v>39113</v>
+        <v>39083</v>
       </c>
       <c r="B116">
         <v>3.786</v>
@@ -1764,7 +1764,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
-        <v>39141</v>
+        <v>39114</v>
       </c>
       <c r="B117">
         <v>3.823</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
-        <v>39171</v>
+        <v>39142</v>
       </c>
       <c r="B118">
         <v>3.9279999999999999</v>
@@ -1792,7 +1792,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
-        <v>39202</v>
+        <v>39173</v>
       </c>
       <c r="B119">
         <v>3.968</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
-        <v>39233</v>
+        <v>39203</v>
       </c>
       <c r="B120">
         <v>4.1029999999999998</v>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
-        <v>39262</v>
+        <v>39234</v>
       </c>
       <c r="B121">
         <v>4.1260000000000003</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
-        <v>39294</v>
+        <v>39264</v>
       </c>
       <c r="B122">
         <v>4.18</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
-        <v>39325</v>
+        <v>39295</v>
       </c>
       <c r="B123">
         <v>3.9660000000000002</v>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
-        <v>39353</v>
+        <v>39326</v>
       </c>
       <c r="B124">
         <v>3.919</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
-        <v>39386</v>
+        <v>39356</v>
       </c>
       <c r="B125">
         <v>4</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
-        <v>39416</v>
+        <v>39387</v>
       </c>
       <c r="B126">
         <v>3.9409999999999998</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
-        <v>39447</v>
+        <v>39417</v>
       </c>
       <c r="B127">
         <v>3.89</v>
@@ -1918,7 +1918,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
-        <v>39478</v>
+        <v>39448</v>
       </c>
       <c r="B128">
         <v>3.8210000000000002</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
-        <v>39507</v>
+        <v>39479</v>
       </c>
       <c r="B129">
         <v>3.8210000000000002</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
-        <v>39538</v>
+        <v>39508</v>
       </c>
       <c r="B130">
         <v>3.6520000000000001</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
-        <v>39568</v>
+        <v>39539</v>
       </c>
       <c r="B131">
         <v>3.863</v>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
-        <v>39598</v>
+        <v>39569</v>
       </c>
       <c r="B132">
         <v>4.024</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
-        <v>39629</v>
+        <v>39600</v>
       </c>
       <c r="B133">
         <v>4.3630000000000004</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
-        <v>39660</v>
+        <v>39630</v>
       </c>
       <c r="B134">
         <v>4.3120000000000003</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
-        <v>39689</v>
+        <v>39661</v>
       </c>
       <c r="B135">
         <v>4.258</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
-        <v>39721</v>
+        <v>39692</v>
       </c>
       <c r="B136">
         <v>3.0830000000000002</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
-        <v>39752</v>
+        <v>39722</v>
       </c>
       <c r="B137">
         <v>2.137</v>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
-        <v>39780</v>
+        <v>39753</v>
       </c>
       <c r="B138">
         <v>1.915</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
-        <v>39813</v>
+        <v>39783</v>
       </c>
       <c r="B139">
         <v>1.583</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
-        <v>39843</v>
+        <v>39814</v>
       </c>
       <c r="B140">
         <v>1.087</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
-        <v>39871</v>
+        <v>39845</v>
       </c>
       <c r="B141">
         <v>0.86299999999999999</v>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
-        <v>39903</v>
+        <v>39873</v>
       </c>
       <c r="B142">
         <v>0.68200000000000005</v>
@@ -2128,7 +2128,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
-        <v>39933</v>
+        <v>39904</v>
       </c>
       <c r="B143">
         <v>0.76200000000000001</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
-        <v>39962</v>
+        <v>39934</v>
       </c>
       <c r="B144">
         <v>0.75700000000000001</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
-        <v>39994</v>
+        <v>39965</v>
       </c>
       <c r="B145">
         <v>0.64300000000000002</v>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
-        <v>40025</v>
+        <v>39995</v>
       </c>
       <c r="B146">
         <v>0.47399999999999998</v>
@@ -2184,7 +2184,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
-        <v>40056</v>
+        <v>40026</v>
       </c>
       <c r="B147">
         <v>0.41399999999999998</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
-        <v>40086</v>
+        <v>40057</v>
       </c>
       <c r="B148">
         <v>0.47099999999999997</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
-        <v>40116</v>
+        <v>40087</v>
       </c>
       <c r="B149">
         <v>0.52500000000000002</v>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
-        <v>40147</v>
+        <v>40118</v>
       </c>
       <c r="B150">
         <v>0.47399999999999998</v>
@@ -2240,7 +2240,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
-        <v>40178</v>
+        <v>40148</v>
       </c>
       <c r="B151">
         <v>0.46800000000000003</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
-        <v>40207</v>
+        <v>40179</v>
       </c>
       <c r="B152">
         <v>0.35599999999999998</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
-        <v>40235</v>
+        <v>40210</v>
       </c>
       <c r="B153">
         <v>0.35099999999999998</v>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
-        <v>40268</v>
+        <v>40238</v>
       </c>
       <c r="B154">
         <v>0.374</v>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
-        <v>40298</v>
+        <v>40269</v>
       </c>
       <c r="B155">
         <v>0.30199999999999999</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
-        <v>40329</v>
+        <v>40299</v>
       </c>
       <c r="B156">
         <v>0.18099999999999999</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
-        <v>40359</v>
+        <v>40330</v>
       </c>
       <c r="B157">
         <v>0.26700000000000002</v>
@@ -2338,7 +2338,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
-        <v>40389</v>
+        <v>40360</v>
       </c>
       <c r="B158">
         <v>0.39600000000000002</v>
@@ -2352,7 +2352,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
-        <v>40421</v>
+        <v>40391</v>
       </c>
       <c r="B159">
         <v>0.38500000000000001</v>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
-        <v>40451</v>
+        <v>40422</v>
       </c>
       <c r="B160">
         <v>0.55700000000000005</v>
@@ -2380,7 +2380,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
-        <v>40480</v>
+        <v>40452</v>
       </c>
       <c r="B161">
         <v>0.745</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
-        <v>40512</v>
+        <v>40483</v>
       </c>
       <c r="B162">
         <v>0.59099999999999997</v>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
-        <v>40543</v>
+        <v>40513</v>
       </c>
       <c r="B163">
         <v>0.42399999999999999</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
-        <v>40574</v>
+        <v>40544</v>
       </c>
       <c r="B164">
         <v>0.76300000000000001</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
-        <v>40602</v>
+        <v>40575</v>
       </c>
       <c r="B165">
         <v>0.84199999999999997</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
-        <v>40633</v>
+        <v>40603</v>
       </c>
       <c r="B166">
         <v>0.97599999999999998</v>
@@ -2464,7 +2464,7 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
-        <v>40662</v>
+        <v>40634</v>
       </c>
       <c r="B167">
         <v>1.1279999999999999</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
-        <v>40694</v>
+        <v>40664</v>
       </c>
       <c r="B168">
         <v>1.131</v>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
-        <v>40724</v>
+        <v>40695</v>
       </c>
       <c r="B169">
         <v>1.2649999999999999</v>
@@ -2506,7 +2506,7 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
-        <v>40753</v>
+        <v>40725</v>
       </c>
       <c r="B170">
         <v>0.99299999999999999</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
-        <v>40786</v>
+        <v>40756</v>
       </c>
       <c r="B171">
         <v>0.54400000000000004</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
-        <v>40816</v>
+        <v>40787</v>
       </c>
       <c r="B172">
         <v>0.41199999999999998</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
-        <v>40847</v>
+        <v>40817</v>
       </c>
       <c r="B173">
         <v>0.30399999999999999</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
-        <v>40877</v>
+        <v>40848</v>
       </c>
       <c r="B174">
         <v>0.11899999999999999</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
-        <v>40907</v>
+        <v>40878</v>
       </c>
       <c r="B175">
         <v>0.1</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
-        <v>40939</v>
+        <v>40909</v>
       </c>
       <c r="B176">
         <v>0.14599999999999999</v>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
-        <v>40968</v>
+        <v>40940</v>
       </c>
       <c r="B177">
         <v>8.6999999999999994E-2</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
-        <v>40998</v>
+        <v>40969</v>
       </c>
       <c r="B178">
         <v>0.17799999999999999</v>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
-        <v>41029</v>
+        <v>41000</v>
       </c>
       <c r="B179">
         <v>2.1999999999999999E-2</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
-        <v>41060</v>
+        <v>41030</v>
       </c>
       <c r="B180">
         <v>3.3000000000000002E-2</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
-        <v>41089</v>
+        <v>41061</v>
       </c>
       <c r="B181">
         <v>5.8000000000000003E-2</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
-        <v>41121</v>
+        <v>41091</v>
       </c>
       <c r="B182">
         <v>-4.1000000000000002E-2</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
-        <v>41152</v>
+        <v>41122</v>
       </c>
       <c r="B183">
         <v>-6.0999999999999999E-2</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
-        <v>41180</v>
+        <v>41153</v>
       </c>
       <c r="B184">
         <v>1.0999999999999999E-2</v>
@@ -2716,7 +2716,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
-        <v>41213</v>
+        <v>41183</v>
       </c>
       <c r="B185">
         <v>0.01</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
-        <v>41243</v>
+        <v>41214</v>
       </c>
       <c r="B186">
         <v>2.1000000000000001E-2</v>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
-        <v>41274</v>
+        <v>41244</v>
       </c>
       <c r="B187">
         <v>0.113</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
-        <v>41305</v>
+        <v>41275</v>
       </c>
       <c r="B188">
         <v>8.5000000000000006E-2</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
-        <v>41333</v>
+        <v>41306</v>
       </c>
       <c r="B189">
         <v>-0.01</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
-        <v>41362</v>
+        <v>41334</v>
       </c>
       <c r="B190">
         <v>-4.0000000000000001E-3</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
-        <v>41394</v>
+        <v>41365</v>
       </c>
       <c r="B191">
         <v>-1.6E-2</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
-        <v>41425</v>
+        <v>41395</v>
       </c>
       <c r="B192">
         <v>4.0000000000000001E-3</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
-        <v>41453</v>
+        <v>41426</v>
       </c>
       <c r="B193">
         <v>7.0000000000000001E-3</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
-        <v>41486</v>
+        <v>41456</v>
       </c>
       <c r="B194">
         <v>4.0000000000000001E-3</v>
@@ -2856,7 +2856,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
-        <v>41516</v>
+        <v>41487</v>
       </c>
       <c r="B195">
         <v>2.3E-2</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
-        <v>41547</v>
+        <v>41518</v>
       </c>
       <c r="B196">
         <v>2.9000000000000001E-2</v>
@@ -2884,7 +2884,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
-        <v>41578</v>
+        <v>41548</v>
       </c>
       <c r="B197">
         <v>3.5000000000000003E-2</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
-        <v>41607</v>
+        <v>41579</v>
       </c>
       <c r="B198">
         <v>6.0999999999999999E-2</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
-        <v>41639</v>
+        <v>41609</v>
       </c>
       <c r="B199">
         <v>0.14399999999999999</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
-        <v>41670</v>
+        <v>41640</v>
       </c>
       <c r="B200">
         <v>8.2000000000000003E-2</v>
@@ -2940,7 +2940,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
-        <v>41698</v>
+        <v>41671</v>
       </c>
       <c r="B201">
         <v>9.8000000000000004E-2</v>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
-        <v>41729</v>
+        <v>41699</v>
       </c>
       <c r="B202">
         <v>0.123</v>
@@ -2968,7 +2968,7 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
-        <v>41759</v>
+        <v>41730</v>
       </c>
       <c r="B203">
         <v>0.11</v>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
-        <v>41789</v>
+        <v>41760</v>
       </c>
       <c r="B204">
         <v>5.8000000000000003E-2</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
-        <v>41820</v>
+        <v>41791</v>
       </c>
       <c r="B205">
         <v>7.0000000000000001E-3</v>
@@ -3010,7 +3010,7 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
-        <v>41851</v>
+        <v>41821</v>
       </c>
       <c r="B206">
         <v>6.0000000000000001E-3</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
-        <v>41880</v>
+        <v>41852</v>
       </c>
       <c r="B207">
         <v>-2.9000000000000001E-2</v>
@@ -3038,7 +3038,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
-        <v>41912</v>
+        <v>41883</v>
       </c>
       <c r="B208">
         <v>-6.7000000000000004E-2</v>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
-        <v>41943</v>
+        <v>41913</v>
       </c>
       <c r="B209">
         <v>-9.6000000000000002E-2</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
-        <v>41971</v>
+        <v>41944</v>
       </c>
       <c r="B210">
         <v>-8.1000000000000003E-2</v>
@@ -3080,7 +3080,7 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
-        <v>42004</v>
+        <v>41974</v>
       </c>
       <c r="B211">
         <v>-9.7000000000000003E-2</v>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
-        <v>42034</v>
+        <v>42005</v>
       </c>
       <c r="B212">
         <v>-0.14899999999999999</v>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
-        <v>42062</v>
+        <v>42036</v>
       </c>
       <c r="B213">
         <v>-0.22</v>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
-        <v>42094</v>
+        <v>42064</v>
       </c>
       <c r="B214">
         <v>-0.21299999999999999</v>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
-        <v>42124</v>
+        <v>42095</v>
       </c>
       <c r="B215">
         <v>-0.26400000000000001</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
-        <v>42153</v>
+        <v>42125</v>
       </c>
       <c r="B216">
         <v>-0.22600000000000001</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
-        <v>42185</v>
+        <v>42156</v>
       </c>
       <c r="B217">
         <v>-0.24</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
-        <v>42216</v>
+        <v>42186</v>
       </c>
       <c r="B218">
         <v>-0.249</v>
@@ -3192,7 +3192,7 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
-        <v>42247</v>
+        <v>42217</v>
       </c>
       <c r="B219">
         <v>-0.23899999999999999</v>
@@ -3206,7 +3206,7 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
-        <v>42277</v>
+        <v>42248</v>
       </c>
       <c r="B220">
         <v>-0.27100000000000002</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
-        <v>42307</v>
+        <v>42278</v>
       </c>
       <c r="B221">
         <v>-0.33600000000000002</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
-        <v>42338</v>
+        <v>42309</v>
       </c>
       <c r="B222">
         <v>-0.372</v>
@@ -3248,7 +3248,7 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
-        <v>42369</v>
+        <v>42339</v>
       </c>
       <c r="B223">
         <v>-0.39600000000000002</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
-        <v>42398</v>
+        <v>42370</v>
       </c>
       <c r="B224">
         <v>-0.41699999999999998</v>
@@ -3276,7 +3276,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
-        <v>42429</v>
+        <v>42401</v>
       </c>
       <c r="B225">
         <v>-0.47699999999999998</v>
@@ -3290,7 +3290,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
-        <v>42460</v>
+        <v>42430</v>
       </c>
       <c r="B226">
         <v>-0.46300000000000002</v>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
-        <v>42489</v>
+        <v>42461</v>
       </c>
       <c r="B227">
         <v>-0.53600000000000003</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
-        <v>42521</v>
+        <v>42491</v>
       </c>
       <c r="B228">
         <v>-0.56499999999999995</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
-        <v>42551</v>
+        <v>42522</v>
       </c>
       <c r="B229">
         <v>-0.65600000000000003</v>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
-        <v>42580</v>
+        <v>42552</v>
       </c>
       <c r="B230">
         <v>-0.64900000000000002</v>
@@ -3360,7 +3360,7 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
-        <v>42613</v>
+        <v>42583</v>
       </c>
       <c r="B231">
         <v>-0.60099999999999998</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
-        <v>42643</v>
+        <v>42614</v>
       </c>
       <c r="B232">
         <v>-0.70199999999999996</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
-        <v>42674</v>
+        <v>42644</v>
       </c>
       <c r="B233">
         <v>-0.71799999999999997</v>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
-        <v>42704</v>
+        <v>42675</v>
       </c>
       <c r="B234">
         <v>-0.76700000000000002</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
-        <v>42734</v>
+        <v>42705</v>
       </c>
       <c r="B235">
         <v>-0.77100000000000002</v>
@@ -3430,7 +3430,7 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
-        <v>42766</v>
+        <v>42736</v>
       </c>
       <c r="B236">
         <v>-0.80400000000000005</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
-        <v>42794</v>
+        <v>42767</v>
       </c>
       <c r="B237">
         <v>-0.84</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
-        <v>42825</v>
+        <v>42795</v>
       </c>
       <c r="B238">
         <v>-0.82799999999999996</v>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
-        <v>42853</v>
+        <v>42826</v>
       </c>
       <c r="B239">
         <v>-0.76200000000000001</v>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
-        <v>42886</v>
+        <v>42856</v>
       </c>
       <c r="B240">
         <v>-0.67900000000000005</v>
@@ -3500,7 +3500,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
-        <v>42916</v>
+        <v>42887</v>
       </c>
       <c r="B241">
         <v>-0.65800000000000003</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
-        <v>42947</v>
+        <v>42917</v>
       </c>
       <c r="B242">
         <v>-0.66200000000000003</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
-        <v>42978</v>
+        <v>42948</v>
       </c>
       <c r="B243">
         <v>-0.67200000000000004</v>
@@ -3542,7 +3542,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
-        <v>43007</v>
+        <v>42979</v>
       </c>
       <c r="B244">
         <v>-0.73299999999999998</v>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
-        <v>43039</v>
+        <v>43009</v>
       </c>
       <c r="B245">
         <v>-0.73099999999999998</v>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
-        <v>43069</v>
+        <v>43040</v>
       </c>
       <c r="B246">
         <v>-0.73699999999999999</v>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
-        <v>43098</v>
+        <v>43070</v>
       </c>
       <c r="B247">
         <v>-0.69399999999999995</v>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
-        <v>43131</v>
+        <v>43101</v>
       </c>
       <c r="B248">
         <v>-0.68400000000000005</v>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
-        <v>43159</v>
+        <v>43132</v>
       </c>
       <c r="B249">
         <v>-0.61</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
-        <v>43189</v>
+        <v>43160</v>
       </c>
       <c r="B250">
         <v>-0.63700000000000001</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
-        <v>43220</v>
+        <v>43191</v>
       </c>
       <c r="B251">
         <v>-0.64600000000000002</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
-        <v>43251</v>
+        <v>43221</v>
       </c>
       <c r="B252">
         <v>-0.60299999999999998</v>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
-        <v>43280</v>
+        <v>43252</v>
       </c>
       <c r="B253">
         <v>-0.60099999999999998</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
-        <v>43312</v>
+        <v>43282</v>
       </c>
       <c r="B254">
         <v>-0.58899999999999997</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
-        <v>43343</v>
+        <v>43313</v>
       </c>
       <c r="B255">
         <v>-0.61399999999999999</v>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
-        <v>43371</v>
+        <v>43344</v>
       </c>
       <c r="B256">
         <v>-0.59899999999999998</v>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
-        <v>43404</v>
+        <v>43374</v>
       </c>
       <c r="B257">
         <v>-0.72199999999999998</v>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
-        <v>43434</v>
+        <v>43405</v>
       </c>
       <c r="B258">
         <v>-0.64700000000000002</v>
@@ -3752,7 +3752,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
-        <v>43465</v>
+        <v>43435</v>
       </c>
       <c r="B259">
         <v>-0.745</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
-        <v>43496</v>
+        <v>43466</v>
       </c>
       <c r="B260">
         <v>-0.54900000000000004</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
-        <v>43524</v>
+        <v>43497</v>
       </c>
       <c r="B261">
         <v>-0.56000000000000005</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
-        <v>43553</v>
+        <v>43525</v>
       </c>
       <c r="B262">
         <v>-0.55000000000000004</v>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
-        <v>43585</v>
+        <v>43556</v>
       </c>
       <c r="B263">
         <v>-0.52900000000000003</v>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
-        <v>43616</v>
+        <v>43586</v>
       </c>
       <c r="B264">
         <v>-0.55100000000000005</v>
@@ -3836,7 +3836,7 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
-        <v>43644</v>
+        <v>43617</v>
       </c>
       <c r="B265">
         <v>-0.56999999999999995</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
-        <v>43677</v>
+        <v>43647</v>
       </c>
       <c r="B266">
         <v>-0.59499999999999997</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
-        <v>43707</v>
+        <v>43678</v>
       </c>
       <c r="B267">
         <v>-0.73699999999999999</v>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
-        <v>43738</v>
+        <v>43709</v>
       </c>
       <c r="B268">
         <v>-0.623</v>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
-        <v>43769</v>
+        <v>43739</v>
       </c>
       <c r="B269">
         <v>-0.60599999999999998</v>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
-        <v>43798</v>
+        <v>43770</v>
       </c>
       <c r="B270">
         <v>-0.59499999999999997</v>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
-        <v>43830</v>
+        <v>43800</v>
       </c>
       <c r="B271">
         <v>-0.61199999999999999</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
-        <v>43861</v>
+        <v>43831</v>
       </c>
       <c r="B272">
         <v>-0.55300000000000005</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
-        <v>43889</v>
+        <v>43862</v>
       </c>
       <c r="B273">
         <v>-0.61199999999999999</v>
@@ -3962,7 +3962,7 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
-        <v>43921</v>
+        <v>43891</v>
       </c>
       <c r="B274">
         <v>-0.69599999999999995</v>
@@ -3976,7 +3976,7 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
-        <v>43951</v>
+        <v>43922</v>
       </c>
       <c r="B275">
         <v>-0.54</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
-        <v>43980</v>
+        <v>43952</v>
       </c>
       <c r="B276">
         <v>-0.53300000000000003</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
-        <v>44012</v>
+        <v>43983</v>
       </c>
       <c r="B277">
         <v>-0.53700000000000003</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
-        <v>44043</v>
+        <v>44013</v>
       </c>
       <c r="B278">
         <v>-0.61099999999999999</v>
@@ -4032,7 +4032,7 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
-        <v>44074</v>
+        <v>44044</v>
       </c>
       <c r="B279">
         <v>-0.58399999999999996</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
-        <v>44104</v>
+        <v>44075</v>
       </c>
       <c r="B280">
         <v>-0.59499999999999997</v>
@@ -4060,7 +4060,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
-        <v>44134</v>
+        <v>44105</v>
       </c>
       <c r="B281">
         <v>-0.72399999999999998</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
-        <v>44165</v>
+        <v>44136</v>
       </c>
       <c r="B282">
         <v>-0.68799999999999994</v>
@@ -4088,7 +4088,7 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
-        <v>44196</v>
+        <v>44166</v>
       </c>
       <c r="B283">
         <v>-0.72899999999999998</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
-        <v>44225</v>
+        <v>44197</v>
       </c>
       <c r="B284">
         <v>-0.61799999999999999</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
-        <v>44253</v>
+        <v>44228</v>
       </c>
       <c r="B285">
         <v>-0.59299999999999997</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
-        <v>44286</v>
+        <v>44256</v>
       </c>
       <c r="B286">
         <v>-0.61399999999999999</v>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
-        <v>44316</v>
+        <v>44287</v>
       </c>
       <c r="B287">
         <v>-0.628</v>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
-        <v>44347</v>
+        <v>44317</v>
       </c>
       <c r="B288">
         <v>-0.63600000000000001</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
-        <v>44377</v>
+        <v>44348</v>
       </c>
       <c r="B289">
         <v>-0.61799999999999999</v>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
-        <v>44407</v>
+        <v>44378</v>
       </c>
       <c r="B290">
         <v>-0.66100000000000003</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
-        <v>44439</v>
+        <v>44409</v>
       </c>
       <c r="B291">
         <v>-0.67800000000000005</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
-        <v>44469</v>
+        <v>44440</v>
       </c>
       <c r="B292">
         <v>-0.72299999999999998</v>
@@ -4228,7 +4228,7 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
-        <v>44498</v>
+        <v>44470</v>
       </c>
       <c r="B293">
         <v>-0.71599999999999997</v>
@@ -4242,7 +4242,7 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
-        <v>44530</v>
+        <v>44501</v>
       </c>
       <c r="B294">
         <v>-0.88800000000000001</v>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
-        <v>44561</v>
+        <v>44531</v>
       </c>
       <c r="B295">
         <v>-0.67900000000000005</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
-        <v>44592</v>
+        <v>44562</v>
       </c>
       <c r="B296">
         <v>-0.67500000000000004</v>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
-        <v>44620</v>
+        <v>44593</v>
       </c>
       <c r="B297">
         <v>-0.72399999999999998</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
-        <v>44651</v>
+        <v>44621</v>
       </c>
       <c r="B298">
         <v>-0.63500000000000001</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
-        <v>44680</v>
+        <v>44652</v>
       </c>
       <c r="B299">
         <v>-0.53400000000000003</v>
@@ -4326,7 +4326,7 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
-        <v>44712</v>
+        <v>44682</v>
       </c>
       <c r="B300">
         <v>-0.27800000000000002</v>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
-        <v>44742</v>
+        <v>44713</v>
       </c>
       <c r="B301">
         <v>-7.4999999999999997E-2</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
-        <v>44771</v>
+        <v>44743</v>
       </c>
       <c r="B302">
         <v>0.13100000000000001</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
-        <v>44804</v>
+        <v>44774</v>
       </c>
       <c r="B303">
         <v>5.5E-2</v>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
-        <v>44834</v>
+        <v>44805</v>
       </c>
       <c r="B304">
         <v>1.1919999999999999</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
-        <v>44865</v>
+        <v>44835</v>
       </c>
       <c r="B305">
         <v>1.49</v>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
-        <v>44895</v>
+        <v>44866</v>
       </c>
       <c r="B306">
         <v>1.8480000000000001</v>
@@ -4424,7 +4424,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
-        <v>44925</v>
+        <v>44896</v>
       </c>
       <c r="B307">
         <v>2.3159999999999998</v>
@@ -4438,7 +4438,7 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
-        <v>44957</v>
+        <v>44927</v>
       </c>
       <c r="B308">
         <v>2.5099999999999998</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
-        <v>44985</v>
+        <v>44958</v>
       </c>
       <c r="B309">
         <v>2.9430000000000001</v>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
-        <v>45016</v>
+        <v>44986</v>
       </c>
       <c r="B310">
         <v>2.8780000000000001</v>
@@ -4480,7 +4480,7 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
-        <v>45044</v>
+        <v>45017</v>
       </c>
       <c r="B311">
         <v>3.024</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
-        <v>45077</v>
+        <v>45047</v>
       </c>
       <c r="B312">
         <v>3.121</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
-        <v>45107</v>
+        <v>45078</v>
       </c>
       <c r="B313">
         <v>3.577</v>
@@ -4522,7 +4522,7 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
-        <v>45138</v>
+        <v>45108</v>
       </c>
       <c r="B314">
         <v>3.5950000000000002</v>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
-        <v>45169</v>
+        <v>45139</v>
       </c>
       <c r="B315">
         <v>3.6179999999999999</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
-        <v>45198</v>
+        <v>45170</v>
       </c>
       <c r="B316">
         <v>3.7349999999999999</v>
@@ -4564,7 +4564,7 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
-        <v>45230</v>
+        <v>45200</v>
       </c>
       <c r="B317">
         <v>3.7469999999999999</v>
@@ -4578,7 +4578,7 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
-        <v>45260</v>
+        <v>45231</v>
       </c>
       <c r="B318">
         <v>3.7040000000000002</v>
@@ -4592,7 +4592,7 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
-        <v>45289</v>
+        <v>45261</v>
       </c>
       <c r="B319">
         <v>3.65</v>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
-        <v>45322</v>
+        <v>45292</v>
       </c>
       <c r="B320">
         <v>3.5880000000000001</v>
@@ -4620,7 +4620,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
-        <v>45351</v>
+        <v>45323</v>
       </c>
       <c r="B321">
         <v>3.6659999999999999</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
-        <v>45380</v>
+        <v>45352</v>
       </c>
       <c r="B322">
         <v>3.6240000000000001</v>
@@ -4648,7 +4648,7 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
-        <v>45412</v>
+        <v>45383</v>
       </c>
       <c r="B323">
         <v>3.589</v>
@@ -4662,7 +4662,7 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
-        <v>45443</v>
+        <v>45413</v>
       </c>
       <c r="B324">
         <v>3.5470000000000002</v>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
-        <v>45471</v>
+        <v>45444</v>
       </c>
       <c r="B325">
         <v>3.3719999999999999</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
-        <v>45504</v>
+        <v>45474</v>
       </c>
       <c r="B326">
         <v>3.2930000000000001</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
-        <v>45534</v>
+        <v>45505</v>
       </c>
       <c r="B327">
         <v>3.1160000000000001</v>
@@ -4718,7 +4718,7 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
-        <v>45565</v>
+        <v>45536</v>
       </c>
       <c r="B328">
         <v>2.8690000000000002</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
-        <v>45596</v>
+        <v>45566</v>
       </c>
       <c r="B329">
         <v>2.7530000000000001</v>
@@ -4746,7 +4746,7 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
-        <v>45625</v>
+        <v>45597</v>
       </c>
       <c r="B330">
         <v>2.5030000000000001</v>
@@ -4760,7 +4760,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
-        <v>45657</v>
+        <v>45627</v>
       </c>
       <c r="B331">
         <v>2.456</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
-        <v>45688</v>
+        <v>45658</v>
       </c>
       <c r="B332">
         <v>2.3410000000000002</v>
@@ -4788,7 +4788,7 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
-        <v>45716</v>
+        <v>45689</v>
       </c>
       <c r="B333">
         <v>2.153</v>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
-        <v>45747</v>
+        <v>45717</v>
       </c>
       <c r="B334">
         <v>2.109</v>
